--- a/data/Daily Act.xlsx
+++ b/data/Daily Act.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abdul\Dropbox\ZYN_ELECTRICAL\XL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7256C82-E628-47FC-BB58-F00BE7ACCE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C96FCF-BB63-41F4-84F4-D3DA9A62AB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="368">
   <si>
     <t>Milling</t>
   </si>
@@ -1123,6 +1123,12 @@
   </si>
   <si>
     <t>Attended By</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Cable / Wiring</t>
   </si>
 </sst>
 </file>
@@ -1264,9 +1270,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1276,21 +1282,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1304,10 +1310,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1588,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:O181"/>
+  <dimension ref="A2:O183"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.08984375" customWidth="1"/>
@@ -1608,1989 +1610,2059 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="9"/>
+      <c r="G2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="N2" s="5" t="s">
+      <c r="L2" s="9"/>
+      <c r="N2" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="O2" s="5"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="8" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="12"/>
+      <c r="H4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="8"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="1" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="12"/>
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="12"/>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="O5" s="7" t="s">
+      <c r="K6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G6" s="8" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="12"/>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="F7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="4" t="s">
+      <c r="G7" s="12"/>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="12"/>
+      <c r="B8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K8" s="12"/>
+      <c r="L8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" s="11" t="s">
+      <c r="C9" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7" t="s">
+      <c r="E9" s="13"/>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="12"/>
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="7" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N7" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="O7" s="7" t="s">
+      <c r="E10" s="13"/>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="K10" s="12"/>
+      <c r="L10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="12"/>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="7" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="O8" s="7" t="s">
+      <c r="E11" s="13"/>
+      <c r="F11" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="O9" s="7" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="4" t="s">
+      <c r="E13" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="K13" s="12"/>
+      <c r="L13" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="I14" s="12"/>
+      <c r="J14" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="12"/>
+      <c r="B15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="F13" s="7" t="s">
+      <c r="E15" s="14"/>
+      <c r="F15" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="8"/>
-      <c r="B14" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="2" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="4" t="s">
+      <c r="G16" s="12"/>
+      <c r="H16" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="9" t="s">
+      <c r="I16" s="12"/>
+      <c r="J16" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="K16" s="12"/>
+      <c r="L16" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" s="16"/>
+      <c r="B17" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I17" s="12"/>
+      <c r="J17" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="K17" s="12"/>
+      <c r="L17" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" s="16"/>
+      <c r="B18" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="I18" s="12"/>
+      <c r="J18" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="16"/>
+      <c r="B19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="I19" s="12"/>
+      <c r="J19" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="16"/>
+      <c r="B20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="I20" s="12"/>
+      <c r="J20" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="16"/>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A22" s="16"/>
+      <c r="B22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A23" s="16"/>
+      <c r="B23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A24" s="16"/>
+      <c r="B24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A25" s="16"/>
+      <c r="B25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A26" s="16"/>
+      <c r="B26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A27" s="16"/>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A28" s="16"/>
+      <c r="B28" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A29" s="16"/>
+      <c r="B29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A30" s="16"/>
+      <c r="B30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="16"/>
+      <c r="B31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="16"/>
+      <c r="B32" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="16"/>
+      <c r="B33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="16"/>
+      <c r="B34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="16"/>
+      <c r="B35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="O15" s="17" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="E35" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" s="14"/>
-      <c r="B21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="14"/>
-      <c r="B22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23" s="14"/>
-      <c r="B23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="14"/>
-      <c r="B24" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="8"/>
-      <c r="H24" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="14"/>
-      <c r="B26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="14"/>
-      <c r="B27" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="14"/>
-      <c r="B28" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="14"/>
-      <c r="B29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G29" s="8"/>
-      <c r="H29" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="14"/>
-      <c r="B30" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" s="8"/>
-      <c r="H30" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="14"/>
-      <c r="B31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="14"/>
-      <c r="B32" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="14"/>
-      <c r="B33" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D33" s="7" t="s">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="16"/>
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="16"/>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="16"/>
+      <c r="B38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="16"/>
+      <c r="B39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="16"/>
+      <c r="B40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="16"/>
+      <c r="B41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="16"/>
+      <c r="B42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="16"/>
+      <c r="B43" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="16"/>
+      <c r="B44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="16"/>
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="13"/>
+      <c r="D45" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="16"/>
+      <c r="B46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="16"/>
+      <c r="B47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="13"/>
+      <c r="D47" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="16"/>
+      <c r="B48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="13"/>
+      <c r="D48" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="16"/>
+      <c r="B49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E33" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="14"/>
-      <c r="B34" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="14"/>
-      <c r="B36" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E36" s="11"/>
-      <c r="F36" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="14"/>
-      <c r="B37" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="14"/>
-      <c r="B38" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="14"/>
-      <c r="B39" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="14"/>
-      <c r="B40" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E40" s="11"/>
-      <c r="F40" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="14"/>
-      <c r="B41" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="14"/>
-      <c r="B42" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="D42" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="14"/>
-      <c r="B43" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="14"/>
-      <c r="B44" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="14"/>
-      <c r="B45" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="14"/>
-      <c r="B46" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="14"/>
-      <c r="B47" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="14"/>
-      <c r="B48" s="7" t="s">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="16"/>
+      <c r="B50" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="2" t="s">
+      <c r="C50" s="13"/>
+      <c r="D50" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="14"/>
-      <c r="B49" s="7" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="16"/>
+      <c r="B51" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="2" t="s">
+      <c r="C51" s="13"/>
+      <c r="D51" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="14"/>
-      <c r="B50" s="7" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="16"/>
+      <c r="B52" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="2" t="s">
+      <c r="C52" s="13"/>
+      <c r="D52" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="14"/>
-      <c r="B51" s="7" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="16"/>
+      <c r="B53" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="11"/>
-      <c r="D51" s="2" t="s">
+      <c r="C53" s="13"/>
+      <c r="D53" s="2" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="14"/>
-      <c r="B52" s="7" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="16"/>
+      <c r="B54" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C52" s="11"/>
-      <c r="D52" s="2" t="s">
+      <c r="C54" s="13"/>
+      <c r="D54" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="14"/>
-      <c r="B53" s="7" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="16"/>
+      <c r="B55" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="11"/>
-      <c r="D53" s="2" t="s">
+      <c r="C55" s="13"/>
+      <c r="D55" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="14"/>
-      <c r="B54" s="7" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="16"/>
+      <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C54" s="11"/>
-      <c r="D54" s="2" t="s">
+      <c r="C56" s="13"/>
+      <c r="D56" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="14"/>
-      <c r="B55" s="7" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="16"/>
+      <c r="B57" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="11"/>
-      <c r="D55" s="2" t="s">
+      <c r="C57" s="13"/>
+      <c r="D57" s="2" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="14"/>
-      <c r="B56" s="7" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="16"/>
+      <c r="B58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="2" t="s">
+      <c r="C58" s="13"/>
+      <c r="D58" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="14"/>
-      <c r="B57" s="7" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="16"/>
+      <c r="B59" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="11"/>
-      <c r="D57" s="2" t="s">
+      <c r="C59" s="13"/>
+      <c r="D59" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="14"/>
-      <c r="B58" s="7" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="16"/>
+      <c r="B60" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C58" s="11"/>
-      <c r="D58" s="2" t="s">
+      <c r="C60" s="13"/>
+      <c r="D60" s="2" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="14"/>
-      <c r="B59" s="7" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="16"/>
+      <c r="B61" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="11"/>
-      <c r="D59" s="2" t="s">
+      <c r="C61" s="13"/>
+      <c r="D61" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="14"/>
-      <c r="B60" s="7" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="16"/>
+      <c r="B62" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C60" s="11"/>
-      <c r="D60" s="2" t="s">
+      <c r="C62" s="13"/>
+      <c r="D62" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="14"/>
-      <c r="B61" s="7" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="16"/>
+      <c r="B63" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="2" t="s">
+      <c r="C63" s="13"/>
+      <c r="D63" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="14"/>
-      <c r="B62" s="7" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="16"/>
+      <c r="B64" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C62" s="11"/>
-      <c r="D62" s="2" t="s">
+      <c r="C64" s="13"/>
+      <c r="D64" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="14"/>
-      <c r="B63" s="7" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="16"/>
+      <c r="B65" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="2" t="s">
+      <c r="C65" s="13"/>
+      <c r="D65" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="14"/>
-      <c r="B64" s="7" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="16"/>
+      <c r="B66" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C64" s="11"/>
-      <c r="D64" s="2" t="s">
+      <c r="C66" s="13"/>
+      <c r="D66" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="14"/>
-      <c r="B65" s="7" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="16"/>
+      <c r="B67" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="2" t="s">
+      <c r="C67" s="13"/>
+      <c r="D67" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="14"/>
-      <c r="B66" s="7" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="16"/>
+      <c r="B68" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C66" s="11"/>
-      <c r="D66" s="2" t="s">
+      <c r="C68" s="13"/>
+      <c r="D68" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="14"/>
-      <c r="B67" s="7" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="16"/>
+      <c r="B69" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C67" s="11"/>
-      <c r="D67" s="2" t="s">
+      <c r="C69" s="13"/>
+      <c r="D69" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="14"/>
-      <c r="B68" s="7" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="16"/>
+      <c r="B70" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C68" s="11"/>
-      <c r="D68" s="2" t="s">
+      <c r="C70" s="13"/>
+      <c r="D70" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="14"/>
-      <c r="B69" s="7" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="16"/>
+      <c r="B71" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C69" s="11"/>
-      <c r="D69" s="2" t="s">
+      <c r="C71" s="13"/>
+      <c r="D71" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="14"/>
-      <c r="B70" s="7" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="16"/>
+      <c r="B72" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C70" s="11"/>
-      <c r="D70" s="2" t="s">
+      <c r="C72" s="13"/>
+      <c r="D72" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="14"/>
-      <c r="B71" s="7" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="16"/>
+      <c r="B73" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="2" t="s">
+      <c r="C73" s="13"/>
+      <c r="D73" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="14"/>
-      <c r="B72" s="7" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="16"/>
+      <c r="B74" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C72" s="11"/>
-      <c r="D72" s="2" t="s">
+      <c r="C74" s="13"/>
+      <c r="D74" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="14"/>
-      <c r="B73" s="7" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="16"/>
+      <c r="B75" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="11"/>
-      <c r="D73" s="2" t="s">
+      <c r="C75" s="13"/>
+      <c r="D75" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="14"/>
-      <c r="B74" s="7" t="s">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="16"/>
+      <c r="B76" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C74" s="11"/>
-      <c r="D74" s="2" t="s">
+      <c r="C76" s="13"/>
+      <c r="D76" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="14"/>
-      <c r="B75" s="7" t="s">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="16"/>
+      <c r="B77" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C75" s="11"/>
-      <c r="D75" s="2" t="s">
+      <c r="C77" s="13"/>
+      <c r="D77" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="14"/>
-      <c r="B76" s="7" t="s">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="16"/>
+      <c r="B78" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C76" s="11"/>
-      <c r="D76" s="2" t="s">
+      <c r="C78" s="13"/>
+      <c r="D78" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="14"/>
-      <c r="B77" s="7" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="16"/>
+      <c r="B79" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C77" s="11"/>
-      <c r="D77" s="2" t="s">
+      <c r="C79" s="13"/>
+      <c r="D79" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="14"/>
-      <c r="B78" s="7" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="16"/>
+      <c r="B80" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C78" s="11"/>
-      <c r="D78" s="2" t="s">
+      <c r="C80" s="13"/>
+      <c r="D80" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="14"/>
-      <c r="B79" s="7" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="16"/>
+      <c r="B81" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C79" s="11"/>
-      <c r="D79" s="2" t="s">
+      <c r="C81" s="13"/>
+      <c r="D81" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="14"/>
-      <c r="B80" s="7" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="16"/>
+      <c r="B82" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C80" s="11"/>
-      <c r="D80" s="2" t="s">
+      <c r="C82" s="13"/>
+      <c r="D82" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="14"/>
-      <c r="B81" s="7" t="s">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="16"/>
+      <c r="B83" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="11"/>
-      <c r="D81" s="2" t="s">
+      <c r="C83" s="13"/>
+      <c r="D83" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="14"/>
-      <c r="B82" s="7" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="16"/>
+      <c r="B84" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="11"/>
-      <c r="D82" s="2" t="s">
+      <c r="C84" s="13"/>
+      <c r="D84" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="14"/>
-      <c r="B83" s="7" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="16"/>
+      <c r="B85" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C85" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="14"/>
-      <c r="B84" s="7" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="16"/>
+      <c r="B86" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C84" s="11"/>
-      <c r="D84" s="2" t="s">
+      <c r="C86" s="13"/>
+      <c r="D86" s="2" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="14"/>
-      <c r="B85" s="7" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="16"/>
+      <c r="B87" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C85" s="11"/>
-      <c r="D85" s="2" t="s">
+      <c r="C87" s="13"/>
+      <c r="D87" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="14"/>
-      <c r="B86" s="7" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="16"/>
+      <c r="B88" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C86" s="11"/>
-      <c r="D86" s="2" t="s">
+      <c r="C88" s="13"/>
+      <c r="D88" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="14"/>
-      <c r="B87" s="7" t="s">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="16"/>
+      <c r="B89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C87" s="11"/>
-      <c r="D87" s="2" t="s">
+      <c r="C89" s="13"/>
+      <c r="D89" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="14"/>
-      <c r="B88" s="7" t="s">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="16"/>
+      <c r="B90" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C88" s="11"/>
-      <c r="D88" s="2" t="s">
+      <c r="C90" s="13"/>
+      <c r="D90" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="14"/>
-      <c r="B89" s="7" t="s">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="16"/>
+      <c r="B91" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="14"/>
-      <c r="B90" s="7" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="16"/>
+      <c r="B92" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="14"/>
-      <c r="B91" s="7" t="s">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="16"/>
+      <c r="B93" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="14"/>
-      <c r="B92" s="7" t="s">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="16"/>
+      <c r="B94" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="14"/>
-      <c r="B93" s="7" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="16"/>
+      <c r="B95" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="14"/>
-      <c r="B94" s="7" t="s">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="16"/>
+      <c r="B96" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="14"/>
-      <c r="B95" s="7" t="s">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="16"/>
+      <c r="B97" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="14"/>
-      <c r="B96" s="7" t="s">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="16"/>
+      <c r="B98" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="14"/>
-      <c r="B97" s="7" t="s">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="16"/>
+      <c r="B99" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="14"/>
-      <c r="B98" s="7" t="s">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="16"/>
+      <c r="B100" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="14"/>
-      <c r="B99" s="7" t="s">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="16"/>
+      <c r="B101" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="14"/>
-      <c r="B100" s="7" t="s">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="16"/>
+      <c r="B102" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="14"/>
-      <c r="B101" s="7" t="s">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="16"/>
+      <c r="B103" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="14"/>
-      <c r="B102" s="7" t="s">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="16"/>
+      <c r="B104" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="14"/>
-      <c r="B103" s="7" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="16"/>
+      <c r="B105" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="14"/>
-      <c r="B104" s="7" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="16"/>
+      <c r="B106" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="14"/>
-      <c r="B105" s="7" t="s">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="16"/>
+      <c r="B107" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="14"/>
-      <c r="B106" s="7" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="16"/>
+      <c r="B108" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="14"/>
-      <c r="B107" s="7" t="s">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="16"/>
+      <c r="B109" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="14"/>
-      <c r="B108" s="7" t="s">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="16"/>
+      <c r="B110" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="14"/>
-      <c r="B109" s="7" t="s">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="16"/>
+      <c r="B111" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="14"/>
-      <c r="B110" s="7" t="s">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="16"/>
+      <c r="B112" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="14"/>
-      <c r="B111" s="7" t="s">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="16"/>
+      <c r="B113" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="14"/>
-      <c r="B112" s="7" t="s">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="16"/>
+      <c r="B114" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="14"/>
-      <c r="B113" s="7" t="s">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="16"/>
+      <c r="B115" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="14"/>
-      <c r="B114" s="7" t="s">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="16"/>
+      <c r="B116" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="14"/>
-      <c r="B115" s="7" t="s">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="16"/>
+      <c r="B117" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="14"/>
-      <c r="B116" s="7" t="s">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="16"/>
+      <c r="B118" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="14"/>
-      <c r="B117" s="7" t="s">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="16"/>
+      <c r="B119" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="14"/>
-      <c r="B118" s="7" t="s">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="16"/>
+      <c r="B120" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="14"/>
-      <c r="B119" s="7" t="s">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="16"/>
+      <c r="B121" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="14"/>
-      <c r="B120" s="7" t="s">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="16"/>
+      <c r="B122" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="14"/>
-      <c r="B121" s="7" t="s">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="16"/>
+      <c r="B123" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="14"/>
-      <c r="B122" s="7" t="s">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="16"/>
+      <c r="B124" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="14"/>
-      <c r="B123" s="7" t="s">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="16"/>
+      <c r="B125" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="14"/>
-      <c r="B124" s="7" t="s">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="16"/>
+      <c r="B126" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="14"/>
-      <c r="B125" s="7" t="s">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="16"/>
+      <c r="B127" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="14"/>
-      <c r="B126" s="7" t="s">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="16"/>
+      <c r="B128" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="14"/>
-      <c r="B127" s="7" t="s">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="16"/>
+      <c r="B129" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="14"/>
-      <c r="B128" s="7" t="s">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="16"/>
+      <c r="B130" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="14"/>
-      <c r="B129" s="7" t="s">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="16"/>
+      <c r="B131" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="14"/>
-      <c r="B130" s="7" t="s">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="16"/>
+      <c r="B132" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="14"/>
-      <c r="B131" s="7" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="16"/>
+      <c r="B133" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="14"/>
-      <c r="B132" s="7" t="s">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="16"/>
+      <c r="B134" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="14"/>
-      <c r="B133" s="7" t="s">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="16"/>
+      <c r="B135" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="14"/>
-      <c r="B134" s="7" t="s">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="16"/>
+      <c r="B136" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="14"/>
-      <c r="B135" s="7" t="s">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="16"/>
+      <c r="B137" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="14"/>
-      <c r="B136" s="7" t="s">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="16"/>
+      <c r="B138" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" s="14"/>
-      <c r="B137" s="7" t="s">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="16"/>
+      <c r="B139" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" s="14"/>
-      <c r="B138" s="7" t="s">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="16"/>
+      <c r="B140" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" s="14"/>
-      <c r="B139" s="7" t="s">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="16"/>
+      <c r="B141" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" s="8" t="s">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B142" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" s="8"/>
-      <c r="B141" s="7" t="s">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="12"/>
+      <c r="B143" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" s="8"/>
-      <c r="B142" s="7" t="s">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="12"/>
+      <c r="B144" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" s="8"/>
-      <c r="B143" s="7" t="s">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="12"/>
+      <c r="B145" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" s="8"/>
-      <c r="B144" s="7" t="s">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="12"/>
+      <c r="B146" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" s="8" t="s">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B147" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" s="8"/>
-      <c r="B146" s="7" t="s">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="12"/>
+      <c r="B148" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" s="8"/>
-      <c r="B147" s="7" t="s">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="12"/>
+      <c r="B149" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" s="8"/>
-      <c r="B148" s="7" t="s">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="12"/>
+      <c r="B150" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" s="8" t="s">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B151" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" s="8"/>
-      <c r="B150" s="7" t="s">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="12"/>
+      <c r="B152" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" s="8"/>
-      <c r="B151" s="7" t="s">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="12"/>
+      <c r="B153" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" s="8"/>
-      <c r="B152" s="7" t="s">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="12"/>
+      <c r="B154" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" s="8"/>
-      <c r="B153" s="7" t="s">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="12"/>
+      <c r="B155" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" s="8"/>
-      <c r="B154" s="7" t="s">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="12"/>
+      <c r="B156" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" s="8"/>
-      <c r="B155" s="7" t="s">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="12"/>
+      <c r="B157" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" s="8"/>
-      <c r="B156" s="7" t="s">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="12"/>
+      <c r="B158" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" s="8"/>
-      <c r="B157" s="7" t="s">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="12"/>
+      <c r="B159" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" s="8"/>
-      <c r="B158" s="7" t="s">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" s="12"/>
+      <c r="B160" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A159" s="8"/>
-      <c r="B159" s="7" t="s">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" s="12"/>
+      <c r="B161" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A160" s="8"/>
-      <c r="B160" s="7" t="s">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" s="12"/>
+      <c r="B162" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A161" s="8"/>
-      <c r="B161" s="7" t="s">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" s="12"/>
+      <c r="B163" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A162" s="8"/>
-      <c r="B162" s="7" t="s">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" s="12"/>
+      <c r="B164" s="1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A163" s="8"/>
-      <c r="B163" s="7" t="s">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" s="12"/>
+      <c r="B165" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A164" s="8"/>
-      <c r="B164" s="7" t="s">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" s="12"/>
+      <c r="B166" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A165" s="8"/>
-      <c r="B165" s="7" t="s">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A167" s="12"/>
+      <c r="B167" s="1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A166" s="8"/>
-      <c r="B166" s="7" t="s">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A168" s="12"/>
+      <c r="B168" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A167" s="8"/>
-      <c r="B167" s="7" t="s">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A169" s="12"/>
+      <c r="B169" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A168" s="8"/>
-      <c r="B168" s="7" t="s">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170" s="12"/>
+      <c r="B170" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A169" s="8"/>
-      <c r="B169" s="7" t="s">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171" s="12"/>
+      <c r="B171" s="1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A170" s="8"/>
-      <c r="B170" s="7" t="s">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172" s="12"/>
+      <c r="B172" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A171" s="8"/>
-      <c r="B171" s="7" t="s">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173" s="12"/>
+      <c r="B173" s="1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A172" s="8"/>
-      <c r="B172" s="7" t="s">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A174" s="12"/>
+      <c r="B174" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A173" s="8"/>
-      <c r="B173" s="7" t="s">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A175" s="12"/>
+      <c r="B175" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A174" s="8"/>
-      <c r="B174" s="7" t="s">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A176" s="12"/>
+      <c r="B176" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A175" s="8"/>
-      <c r="B175" s="7" t="s">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177" s="12"/>
+      <c r="B177" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A176" s="8"/>
-      <c r="B176" s="7" t="s">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178" s="12"/>
+      <c r="B178" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A177" s="8"/>
-      <c r="B177" s="7" t="s">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179" s="12"/>
+      <c r="B179" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A178" s="8"/>
-      <c r="B178" s="7" t="s">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180" s="12"/>
+      <c r="B180" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A179" s="8"/>
-      <c r="B179" s="7" t="s">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181" s="12"/>
+      <c r="B181" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A180" s="8"/>
-      <c r="B180" s="7" t="s">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182" s="12"/>
+      <c r="B182" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A181" s="8"/>
-      <c r="B181" s="7" t="s">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183" s="12"/>
+      <c r="B183" s="1" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="C85:C90"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E13:E34"/>
+    <mergeCell ref="A151:A183"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="C9:C14"/>
+    <mergeCell ref="C15:C34"/>
+    <mergeCell ref="C49:C84"/>
+    <mergeCell ref="C35:C48"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="A147:A150"/>
+    <mergeCell ref="A16:A141"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="K9:K20"/>
+    <mergeCell ref="I5:I21"/>
+    <mergeCell ref="E35:E45"/>
+    <mergeCell ref="E7:E12"/>
+    <mergeCell ref="G6:G11"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="G12:G32"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -3598,30 +3670,6 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="K9:K18"/>
-    <mergeCell ref="I5:I19"/>
-    <mergeCell ref="E33:E43"/>
-    <mergeCell ref="E7:E12"/>
-    <mergeCell ref="G6:G11"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="G12:G30"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="C83:C88"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E13:E32"/>
-    <mergeCell ref="A149:A181"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="C9:C14"/>
-    <mergeCell ref="C15:C32"/>
-    <mergeCell ref="C47:C82"/>
-    <mergeCell ref="C33:C46"/>
-    <mergeCell ref="A140:A144"/>
-    <mergeCell ref="A145:A148"/>
-    <mergeCell ref="A16:A139"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
